--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/81.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/81.xlsx
@@ -426,13 +426,13 @@
         <v>-12.38603644708903</v>
       </c>
       <c r="E2">
-        <v>-8.97489414302933</v>
+        <v>-5.606809900506448</v>
       </c>
       <c r="F2">
-        <v>2.946663961267165</v>
+        <v>3.353860091421294</v>
       </c>
       <c r="G2">
-        <v>-11.03412226506106</v>
+        <v>-10.87267026965635</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.78895059248595</v>
       </c>
       <c r="E3">
-        <v>-9.496356981960586</v>
+        <v>-5.0849394989145</v>
       </c>
       <c r="F3">
-        <v>2.693472145448114</v>
+        <v>2.796386106951116</v>
       </c>
       <c r="G3">
-        <v>-10.49643339020926</v>
+        <v>-9.532051611346324</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.10738144088328</v>
       </c>
       <c r="E4">
-        <v>-9.390884293847936</v>
+        <v>-6.813073107351624</v>
       </c>
       <c r="F4">
-        <v>2.852656761832595</v>
+        <v>3.532522706859764</v>
       </c>
       <c r="G4">
-        <v>-9.94565130774963</v>
+        <v>-8.790827086194584</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.40520295942612</v>
       </c>
       <c r="E5">
-        <v>-9.376678470885874</v>
+        <v>-7.727245212228055</v>
       </c>
       <c r="F5">
-        <v>2.905036251279839</v>
+        <v>3.789106820749686</v>
       </c>
       <c r="G5">
-        <v>-10.50099532196237</v>
+        <v>-9.533561220112231</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.693155383359976</v>
       </c>
       <c r="E6">
-        <v>-12.15901365746461</v>
+        <v>-9.80981795277153</v>
       </c>
       <c r="F6">
-        <v>2.779438869949998</v>
+        <v>3.516406915464252</v>
       </c>
       <c r="G6">
-        <v>-8.601500297349203</v>
+        <v>-7.942638834668991</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.992692595039696</v>
       </c>
       <c r="E7">
-        <v>-11.80243255715263</v>
+        <v>-7.946242215238993</v>
       </c>
       <c r="F7">
-        <v>3.409894774121372</v>
+        <v>3.600110524212973</v>
       </c>
       <c r="G7">
-        <v>-8.564074580027743</v>
+        <v>-9.594309730757857</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.300924886539326</v>
       </c>
       <c r="E8">
-        <v>-12.10954460740482</v>
+        <v>-10.02448573463113</v>
       </c>
       <c r="F8">
-        <v>3.04903154422934</v>
+        <v>3.978426193293149</v>
       </c>
       <c r="G8">
-        <v>-7.488759730689372</v>
+        <v>-7.503104324511034</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.628818162185984</v>
       </c>
       <c r="E9">
-        <v>-12.91226191000447</v>
+        <v>-11.11034587456037</v>
       </c>
       <c r="F9">
-        <v>3.072921747963744</v>
+        <v>4.351781695446167</v>
       </c>
       <c r="G9">
-        <v>-6.770411075213995</v>
+        <v>-5.574423530423651</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.962312771233368</v>
       </c>
       <c r="E10">
-        <v>-14.20264152154212</v>
+        <v>-10.02398307401628</v>
       </c>
       <c r="F10">
-        <v>3.706796873206552</v>
+        <v>4.457243839767111</v>
       </c>
       <c r="G10">
-        <v>-6.503243429103732</v>
+        <v>-6.417010338896796</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.300826185791755</v>
       </c>
       <c r="E11">
-        <v>-13.7521670411551</v>
+        <v>-10.0977292732312</v>
       </c>
       <c r="F11">
-        <v>3.510746750522472</v>
+        <v>4.159755769493219</v>
       </c>
       <c r="G11">
-        <v>-4.692739179131713</v>
+        <v>-4.829739485183373</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.639457659652099</v>
       </c>
       <c r="E12">
-        <v>-15.00309005866393</v>
+        <v>-12.98587225499915</v>
       </c>
       <c r="F12">
-        <v>3.268726396230931</v>
+        <v>4.670397986337937</v>
       </c>
       <c r="G12">
-        <v>-4.197196859540366</v>
+        <v>-4.052926595484466</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.967048358177747</v>
       </c>
       <c r="E13">
-        <v>-14.85236885826663</v>
+        <v>-11.88250050608225</v>
       </c>
       <c r="F13">
-        <v>3.741139535982856</v>
+        <v>4.521051351100167</v>
       </c>
       <c r="G13">
-        <v>-3.945767546923798</v>
+        <v>-3.384299023463404</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.294722399460981</v>
       </c>
       <c r="E14">
-        <v>-15.88366541487745</v>
+        <v>-13.63606149607245</v>
       </c>
       <c r="F14">
-        <v>3.483977369433799</v>
+        <v>4.928578475790623</v>
       </c>
       <c r="G14">
-        <v>-3.90810347032351</v>
+        <v>-3.672574707932061</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.619776886131265</v>
       </c>
       <c r="E15">
-        <v>-16.78095989712729</v>
+        <v>-14.75483005661542</v>
       </c>
       <c r="F15">
-        <v>4.049224182536954</v>
+        <v>5.200633812768473</v>
       </c>
       <c r="G15">
-        <v>-3.033751977401057</v>
+        <v>-2.083377116714781</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.950735816972397</v>
       </c>
       <c r="E16">
-        <v>-17.7796016276688</v>
+        <v>-16.52292744817024</v>
       </c>
       <c r="F16">
-        <v>3.741833199173819</v>
+        <v>4.708418014249892</v>
       </c>
       <c r="G16">
-        <v>-2.601659573615382</v>
+        <v>-2.185821948427528</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.301247828177343</v>
       </c>
       <c r="E17">
-        <v>-18.09619177401904</v>
+        <v>-16.23594899335615</v>
       </c>
       <c r="F17">
-        <v>3.528764572722427</v>
+        <v>4.899411363945974</v>
       </c>
       <c r="G17">
-        <v>-2.050198829320205</v>
+        <v>-1.724884761358183</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.679154467002088</v>
       </c>
       <c r="E18">
-        <v>-19.19372179146604</v>
+        <v>-16.94559709815016</v>
       </c>
       <c r="F18">
-        <v>4.259334446338305</v>
+        <v>4.995952492845247</v>
       </c>
       <c r="G18">
-        <v>-2.07007203419245</v>
+        <v>-1.825290297018739</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.107531290227542</v>
       </c>
       <c r="E19">
-        <v>-20.08851655606365</v>
+        <v>-17.24508772664743</v>
       </c>
       <c r="F19">
-        <v>4.066233184068773</v>
+        <v>5.658636812395814</v>
       </c>
       <c r="G19">
-        <v>-1.660137111701117</v>
+        <v>-1.25966703890656</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.6055187217803465</v>
       </c>
       <c r="E20">
-        <v>-20.75087380679556</v>
+        <v>-18.56555904796606</v>
       </c>
       <c r="F20">
-        <v>4.214672355816997</v>
+        <v>5.66840669418816</v>
       </c>
       <c r="G20">
-        <v>-1.197044759485706</v>
+        <v>-0.8712804573303428</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.193767541017706</v>
       </c>
       <c r="E21">
-        <v>-20.11124043863414</v>
+        <v>-18.31422421206635</v>
       </c>
       <c r="F21">
-        <v>4.573039665186298</v>
+        <v>4.590140521661213</v>
       </c>
       <c r="G21">
-        <v>-1.292083900827103</v>
+        <v>-1.424439511487165</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.1029055671583953</v>
       </c>
       <c r="E22">
-        <v>-22.12749820580929</v>
+        <v>-19.28283763146299</v>
       </c>
       <c r="F22">
-        <v>4.363064016387758</v>
+        <v>5.349556014820905</v>
       </c>
       <c r="G22">
-        <v>-0.9123808802003945</v>
+        <v>0.1931327655472079</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.268187542108193</v>
       </c>
       <c r="E23">
-        <v>-21.82321192333789</v>
+        <v>-18.44558618608085</v>
       </c>
       <c r="F23">
-        <v>4.040825790067379</v>
+        <v>5.259199257521423</v>
       </c>
       <c r="G23">
-        <v>-0.6764118152522228</v>
+        <v>0.0909627091142205</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.2911245836294123</v>
       </c>
       <c r="E24">
-        <v>-22.10841521634097</v>
+        <v>-20.47316513827517</v>
       </c>
       <c r="F24">
-        <v>4.091702342600871</v>
+        <v>5.289376773740122</v>
       </c>
       <c r="G24">
-        <v>-0.6100022717344429</v>
+        <v>-0.3055578828519859</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.1658805247603629</v>
       </c>
       <c r="E25">
-        <v>-22.89258841787921</v>
+        <v>-19.94069810750528</v>
       </c>
       <c r="F25">
-        <v>4.175017943400309</v>
+        <v>5.170972584678207</v>
       </c>
       <c r="G25">
-        <v>0.1624241451249283</v>
+        <v>0.7378333758511926</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.1010603330085651</v>
       </c>
       <c r="E26">
-        <v>-22.92112233260154</v>
+        <v>-22.16066474944147</v>
       </c>
       <c r="F26">
-        <v>3.877347746946142</v>
+        <v>4.87808042897092</v>
       </c>
       <c r="G26">
-        <v>0.1645064782691299</v>
+        <v>0.7153481505484627</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.4971384067300128</v>
       </c>
       <c r="E27">
-        <v>-22.18493284164857</v>
+        <v>-21.01210335840203</v>
       </c>
       <c r="F27">
-        <v>3.78807424449282</v>
+        <v>4.90799029888991</v>
       </c>
       <c r="G27">
-        <v>-0.09508001855620241</v>
+        <v>0.02123599896609075</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.006750178826902</v>
       </c>
       <c r="E28">
-        <v>-23.27317043043184</v>
+        <v>-20.27808300649874</v>
       </c>
       <c r="F28">
-        <v>4.0321296608857</v>
+        <v>5.255182979319869</v>
       </c>
       <c r="G28">
-        <v>0.4336339673386418</v>
+        <v>0.8973321493877392</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.603530696460421</v>
       </c>
       <c r="E29">
-        <v>-22.51137694743951</v>
+        <v>-20.05035057712701</v>
       </c>
       <c r="F29">
-        <v>3.861521773733155</v>
+        <v>4.612301318535957</v>
       </c>
       <c r="G29">
-        <v>0.1284281529821525</v>
+        <v>1.415048503001124</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.264094511400462</v>
       </c>
       <c r="E30">
-        <v>-22.09224856413359</v>
+        <v>-21.33175475318146</v>
       </c>
       <c r="F30">
-        <v>3.974951542514674</v>
+        <v>4.924703147415542</v>
       </c>
       <c r="G30">
-        <v>-0.1902979293567203</v>
+        <v>0.5363833692410016</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.966861076097986</v>
       </c>
       <c r="E31">
-        <v>-21.1711977072395</v>
+        <v>-20.85206708697096</v>
       </c>
       <c r="F31">
-        <v>4.088023393759305</v>
+        <v>4.609061056232967</v>
       </c>
       <c r="G31">
-        <v>-0.1598574631231217</v>
+        <v>0.8988814847001181</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.68435510644853</v>
       </c>
       <c r="E32">
-        <v>-21.56963549280438</v>
+        <v>-20.82316183738</v>
       </c>
       <c r="F32">
-        <v>4.002298976262483</v>
+        <v>4.724063444988518</v>
       </c>
       <c r="G32">
-        <v>-0.1572090266917048</v>
+        <v>0.2437046592051145</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.406578710261613</v>
       </c>
       <c r="E33">
-        <v>-21.96407916429449</v>
+        <v>-20.23225484954112</v>
       </c>
       <c r="F33">
-        <v>3.887945906932262</v>
+        <v>4.581506157010237</v>
       </c>
       <c r="G33">
-        <v>-0.5288872849312202</v>
+        <v>-0.9256826521771861</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.118986022834471</v>
       </c>
       <c r="E34">
-        <v>-21.14662167879988</v>
+        <v>-19.77331212275976</v>
       </c>
       <c r="F34">
-        <v>3.79783937516742</v>
+        <v>5.314928284979822</v>
       </c>
       <c r="G34">
-        <v>-0.2755047504464821</v>
+        <v>-0.2509702974549433</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.812697637228673</v>
       </c>
       <c r="E35">
-        <v>-19.75207357966378</v>
+        <v>-18.42709642670753</v>
       </c>
       <c r="F35">
-        <v>4.390012356244876</v>
+        <v>5.071913363373385</v>
       </c>
       <c r="G35">
-        <v>-1.218652690220529</v>
+        <v>-0.350227073813372</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.490538823949044</v>
       </c>
       <c r="E36">
-        <v>-18.70673875362919</v>
+        <v>-18.9675199863089</v>
       </c>
       <c r="F36">
-        <v>4.393059406426182</v>
+        <v>4.755020144517613</v>
       </c>
       <c r="G36">
-        <v>-1.018550075644822</v>
+        <v>-0.4615209937525908</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.141117757198593</v>
       </c>
       <c r="E37">
-        <v>-19.46041268272577</v>
+        <v>-18.47440086619165</v>
       </c>
       <c r="F37">
-        <v>4.15213339292221</v>
+        <v>4.680188456307184</v>
       </c>
       <c r="G37">
-        <v>-1.598812566131657</v>
+        <v>-1.445408506932909</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.77090463729434</v>
       </c>
       <c r="E38">
-        <v>-18.75141214971486</v>
+        <v>-16.01203859604689</v>
       </c>
       <c r="F38">
-        <v>4.499105938229922</v>
+        <v>5.418748126266455</v>
       </c>
       <c r="G38">
-        <v>-1.821767876564954</v>
+        <v>-0.8454350283052525</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.376901413560368</v>
       </c>
       <c r="E39">
-        <v>-17.32250651828257</v>
+        <v>-16.54964091634148</v>
       </c>
       <c r="F39">
-        <v>4.667881477638304</v>
+        <v>5.576645189741683</v>
       </c>
       <c r="G39">
-        <v>-1.142675670094255</v>
+        <v>-1.902806720820773</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.951689117527444</v>
       </c>
       <c r="E40">
-        <v>-16.97625033870808</v>
+        <v>-15.24610155933754</v>
       </c>
       <c r="F40">
-        <v>4.59348214114279</v>
+        <v>5.457746884434151</v>
       </c>
       <c r="G40">
-        <v>-1.534131127385377</v>
+        <v>-0.6023151849922551</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.498424277179431</v>
       </c>
       <c r="E41">
-        <v>-16.78460531870347</v>
+        <v>-15.13743629704948</v>
       </c>
       <c r="F41">
-        <v>4.578630147067798</v>
+        <v>5.802644774992639</v>
       </c>
       <c r="G41">
-        <v>-2.221860547168034</v>
+        <v>-2.716035611451662</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.00599467572134</v>
       </c>
       <c r="E42">
-        <v>-16.34450104379401</v>
+        <v>-14.70004910654463</v>
       </c>
       <c r="F42">
-        <v>4.575000293109611</v>
+        <v>5.870658609237101</v>
       </c>
       <c r="G42">
-        <v>-2.358698636488269</v>
+        <v>-2.096314728682253</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.47497361479876</v>
       </c>
       <c r="E43">
-        <v>-14.6078086194824</v>
+        <v>-13.99896434609913</v>
       </c>
       <c r="F43">
-        <v>4.813161156085227</v>
+        <v>6.087564555121603</v>
       </c>
       <c r="G43">
-        <v>-2.693937719977027</v>
+        <v>-2.422231315932422</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.90305697962173</v>
       </c>
       <c r="E44">
-        <v>-14.48255102843023</v>
+        <v>-13.0886278587072</v>
       </c>
       <c r="F44">
-        <v>4.472057824900132</v>
+        <v>5.938520407713682</v>
       </c>
       <c r="G44">
-        <v>-3.407631748424188</v>
+        <v>-2.757738553609861</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.28425854424943</v>
       </c>
       <c r="E45">
-        <v>-14.01968211468422</v>
+        <v>-14.10667410037157</v>
       </c>
       <c r="F45">
-        <v>4.916664256188771</v>
+        <v>5.587194254844426</v>
       </c>
       <c r="G45">
-        <v>-3.444752895556036</v>
+        <v>-1.687733819316481</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.62537583419243</v>
       </c>
       <c r="E46">
-        <v>-13.72845142277693</v>
+        <v>-11.34275168910802</v>
       </c>
       <c r="F46">
-        <v>4.719682914426413</v>
+        <v>5.633793217700315</v>
       </c>
       <c r="G46">
-        <v>-3.364641004051212</v>
+        <v>-2.174380703043806</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.92234023397607</v>
       </c>
       <c r="E47">
-        <v>-12.89495408234715</v>
+        <v>-12.00274054793391</v>
       </c>
       <c r="F47">
-        <v>4.954511660155943</v>
+        <v>5.527078362000259</v>
       </c>
       <c r="G47">
-        <v>-3.631851687253486</v>
+        <v>-3.990062646239246</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.17850891478151</v>
       </c>
       <c r="E48">
-        <v>-13.00257779561345</v>
+        <v>-11.56126414540014</v>
       </c>
       <c r="F48">
-        <v>5.234946385132384</v>
+        <v>5.627448891803065</v>
       </c>
       <c r="G48">
-        <v>-3.788976799638375</v>
+        <v>-3.950412242315395</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.39671171942572</v>
       </c>
       <c r="E49">
-        <v>-11.59685342262642</v>
+        <v>-11.35214827267394</v>
       </c>
       <c r="F49">
-        <v>5.151700467393225</v>
+        <v>6.259876509839161</v>
       </c>
       <c r="G49">
-        <v>-3.479738740815054</v>
+        <v>-3.768656671118328</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.57238149585846</v>
       </c>
       <c r="E50">
-        <v>-12.11832079003169</v>
+        <v>-11.26982967216251</v>
       </c>
       <c r="F50">
-        <v>5.331158103201245</v>
+        <v>5.81659722410766</v>
       </c>
       <c r="G50">
-        <v>-4.387149341492668</v>
+        <v>-2.781839325135755</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.71380102433212</v>
       </c>
       <c r="E51">
-        <v>-10.01053803468751</v>
+        <v>-10.59783130026827</v>
       </c>
       <c r="F51">
-        <v>5.286627460270919</v>
+        <v>6.100273795093005</v>
       </c>
       <c r="G51">
-        <v>-4.21212410937694</v>
+        <v>-4.46100099138273</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.81564258430897</v>
       </c>
       <c r="E52">
-        <v>-9.633628614555098</v>
+        <v>-9.145884793084955</v>
       </c>
       <c r="F52">
-        <v>5.385680346752079</v>
+        <v>6.079302361360756</v>
       </c>
       <c r="G52">
-        <v>-4.462619848151434</v>
+        <v>-4.199226223955939</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.87955920110661</v>
       </c>
       <c r="E53">
-        <v>-11.27717485700295</v>
+        <v>-10.37325521727988</v>
       </c>
       <c r="F53">
-        <v>5.369594645768961</v>
+        <v>6.266958842693007</v>
       </c>
       <c r="G53">
-        <v>-4.235407176154634</v>
+        <v>-3.717859660363751</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.90616954993467</v>
       </c>
       <c r="E54">
-        <v>-8.355136247287581</v>
+        <v>-10.32320652254711</v>
       </c>
       <c r="F54">
-        <v>5.03518880690026</v>
+        <v>5.94197605402117</v>
       </c>
       <c r="G54">
-        <v>-5.365402306165147</v>
+        <v>-4.086204199245221</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.89180958766192</v>
       </c>
       <c r="E55">
-        <v>-9.414187821091408</v>
+        <v>-7.623986947905155</v>
       </c>
       <c r="F55">
-        <v>5.267634075227054</v>
+        <v>6.031344578829419</v>
       </c>
       <c r="G55">
-        <v>-5.674623812260772</v>
+        <v>-4.627802828378909</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.84374522633757</v>
       </c>
       <c r="E56">
-        <v>-8.371941414330045</v>
+        <v>-7.299748208955958</v>
       </c>
       <c r="F56">
-        <v>5.279557797064397</v>
+        <v>6.350174670019773</v>
       </c>
       <c r="G56">
-        <v>-5.536524405090074</v>
+        <v>-3.723153222681046</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.75771183692764</v>
       </c>
       <c r="E57">
-        <v>-7.537275727606283</v>
+        <v>-7.356956421094857</v>
       </c>
       <c r="F57">
-        <v>5.537532404748076</v>
+        <v>6.234435858013542</v>
       </c>
       <c r="G57">
-        <v>-6.006012731287357</v>
+        <v>-4.57155997021223</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.64006200402984</v>
       </c>
       <c r="E58">
-        <v>-7.212167521647613</v>
+        <v>-8.539680620048163</v>
       </c>
       <c r="F58">
-        <v>5.523473847336719</v>
+        <v>5.956196149435901</v>
       </c>
       <c r="G58">
-        <v>-5.437135206910074</v>
+        <v>-5.723040540772613</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.49558797497771</v>
       </c>
       <c r="E59">
-        <v>-6.43064800587787</v>
+        <v>-5.586504223056054</v>
       </c>
       <c r="F59">
-        <v>5.675715496987913</v>
+        <v>6.393991061582236</v>
       </c>
       <c r="G59">
-        <v>-5.333902465358982</v>
+        <v>-4.718180721601012</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.32459362013349</v>
       </c>
       <c r="E60">
-        <v>-7.136881641270093</v>
+        <v>-4.898502224018712</v>
       </c>
       <c r="F60">
-        <v>5.44534329970443</v>
+        <v>5.716316965542035</v>
       </c>
       <c r="G60">
-        <v>-5.904031375950108</v>
+        <v>-5.968914757974284</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.13575996198175</v>
       </c>
       <c r="E61">
-        <v>-6.796077744400837</v>
+        <v>-5.376532468742402</v>
       </c>
       <c r="F61">
-        <v>5.433170936038362</v>
+        <v>5.791177160458941</v>
       </c>
       <c r="G61">
-        <v>-5.633669053394448</v>
+        <v>-5.631043790781806</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.92851393730254</v>
       </c>
       <c r="E62">
-        <v>-7.159637223158636</v>
+        <v>-5.942890598985704</v>
       </c>
       <c r="F62">
-        <v>5.437201467593155</v>
+        <v>5.951864713757175</v>
       </c>
       <c r="G62">
-        <v>-5.806350419268372</v>
+        <v>-6.052731149937552</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.70708638560721</v>
       </c>
       <c r="E63">
-        <v>-6.324613786988269</v>
+        <v>-6.029760315874844</v>
       </c>
       <c r="F63">
-        <v>5.374269745631338</v>
+        <v>6.15660146338744</v>
       </c>
       <c r="G63">
-        <v>-5.998709667827725</v>
+        <v>-5.71405903072457</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.47857040304814</v>
       </c>
       <c r="E64">
-        <v>-5.247597756796012</v>
+        <v>-4.657170787201943</v>
       </c>
       <c r="F64">
-        <v>5.135518160349264</v>
+        <v>6.597023743647489</v>
       </c>
       <c r="G64">
-        <v>-6.1500843626109</v>
+        <v>-6.11651543084269</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.24086316136174</v>
       </c>
       <c r="E65">
-        <v>-4.954537561389625</v>
+        <v>-5.266685274738343</v>
       </c>
       <c r="F65">
-        <v>5.211570885820497</v>
+        <v>5.940523795696713</v>
       </c>
       <c r="G65">
-        <v>-6.616917631285687</v>
+        <v>-6.458680175599603</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.00202909971717</v>
       </c>
       <c r="E66">
-        <v>-6.165551137468848</v>
+        <v>-4.050029220045563</v>
       </c>
       <c r="F66">
-        <v>5.3214088095858</v>
+        <v>6.292201531279196</v>
       </c>
       <c r="G66">
-        <v>-5.931386413741106</v>
+        <v>-5.604840822838475</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.76160996138008</v>
       </c>
       <c r="E67">
-        <v>-6.387247110988358</v>
+        <v>-4.454584973994802</v>
       </c>
       <c r="F67">
-        <v>5.343148340687038</v>
+        <v>6.179679225987224</v>
       </c>
       <c r="G67">
-        <v>-6.702336327289962</v>
+        <v>-6.476219445866661</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.52103611721992</v>
       </c>
       <c r="E68">
-        <v>-6.152196667620228</v>
+        <v>-4.653765374748176</v>
       </c>
       <c r="F68">
-        <v>5.432013247014176</v>
+        <v>5.349413481288516</v>
       </c>
       <c r="G68">
-        <v>-6.529880078512709</v>
+        <v>-5.76538572876543</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.28750995443245</v>
       </c>
       <c r="E69">
-        <v>-6.378996231346382</v>
+        <v>-5.811211631790665</v>
       </c>
       <c r="F69">
-        <v>5.277232916780532</v>
+        <v>5.715452262112205</v>
       </c>
       <c r="G69">
-        <v>-6.202765073777322</v>
+        <v>-5.451681744009632</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.05568438800137</v>
       </c>
       <c r="E70">
-        <v>-6.752020220780213</v>
+        <v>-4.164649425653708</v>
       </c>
       <c r="F70">
-        <v>4.618910123321085</v>
+        <v>5.441661183451033</v>
       </c>
       <c r="G70">
-        <v>-6.201027037369204</v>
+        <v>-5.383825492091191</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.833415306658438</v>
       </c>
       <c r="E71">
-        <v>-5.778357552865017</v>
+        <v>-5.001796716133673</v>
       </c>
       <c r="F71">
-        <v>4.94078568098683</v>
+        <v>5.749332482761201</v>
       </c>
       <c r="G71">
-        <v>-6.848589608123885</v>
+        <v>-6.347227349474499</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.619579434839851</v>
       </c>
       <c r="E72">
-        <v>-6.705037302950632</v>
+        <v>-5.69293694765833</v>
       </c>
       <c r="F72">
-        <v>4.770453358663571</v>
+        <v>5.871840053850019</v>
       </c>
       <c r="G72">
-        <v>-5.932233913399159</v>
+        <v>-5.674974730087935</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.411790715653426</v>
       </c>
       <c r="E73">
-        <v>-7.01438641936261</v>
+        <v>-4.555651456897989</v>
       </c>
       <c r="F73">
-        <v>4.509002516495503</v>
+        <v>5.327067390821665</v>
       </c>
       <c r="G73">
-        <v>-6.350190287732147</v>
+        <v>-5.950703446962754</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.213001517801462</v>
       </c>
       <c r="E74">
-        <v>-5.967570782327507</v>
+        <v>-5.625204561925605</v>
       </c>
       <c r="F74">
-        <v>4.957693325340061</v>
+        <v>5.476185972407613</v>
       </c>
       <c r="G74">
-        <v>-5.743761245302911</v>
+        <v>-4.463877855456357</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.015152581659169</v>
       </c>
       <c r="E75">
-        <v>-7.211221070580009</v>
+        <v>-6.011315841241602</v>
       </c>
       <c r="F75">
-        <v>4.890626547233031</v>
+        <v>5.764155970129714</v>
       </c>
       <c r="G75">
-        <v>-5.602692278783488</v>
+        <v>-5.658322686025401</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.818347301242015</v>
       </c>
       <c r="E76">
-        <v>-6.560972959344615</v>
+        <v>-6.75600980638097</v>
       </c>
       <c r="F76">
-        <v>4.45262575331769</v>
+        <v>5.538545976533957</v>
       </c>
       <c r="G76">
-        <v>-5.889892035951881</v>
+        <v>-5.600414623452469</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.618593944111566</v>
       </c>
       <c r="E77">
-        <v>-8.407494463764264</v>
+        <v>-6.376419529636017</v>
       </c>
       <c r="F77">
-        <v>4.538883879708015</v>
+        <v>5.113094468292557</v>
       </c>
       <c r="G77">
-        <v>-6.286008741362297</v>
+        <v>-4.734928771484185</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.40670968595812</v>
       </c>
       <c r="E78">
-        <v>-9.703647879661698</v>
+        <v>-7.339843317819871</v>
       </c>
       <c r="F78">
-        <v>4.575705042241982</v>
+        <v>5.236715384639929</v>
       </c>
       <c r="G78">
-        <v>-5.024829933812623</v>
+        <v>-4.297774543568964</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.180933541380783</v>
       </c>
       <c r="E79">
-        <v>-8.783063455590407</v>
+        <v>-9.600072622158262</v>
       </c>
       <c r="F79">
-        <v>4.467415982861979</v>
+        <v>5.034222746291841</v>
       </c>
       <c r="G79">
-        <v>-5.640104753922792</v>
+        <v>-4.03855882784403</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.930749747363079</v>
       </c>
       <c r="E80">
-        <v>-9.262157891705899</v>
+        <v>-8.255315094736503</v>
       </c>
       <c r="F80">
-        <v>4.449976213321159</v>
+        <v>5.175741123189595</v>
       </c>
       <c r="G80">
-        <v>-4.675123766317251</v>
+        <v>-3.985596720306769</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.652827946521814</v>
       </c>
       <c r="E81">
-        <v>-9.984884229434057</v>
+        <v>-9.329777065588432</v>
       </c>
       <c r="F81">
-        <v>4.652427675315446</v>
+        <v>5.061052308205301</v>
       </c>
       <c r="G81">
-        <v>-4.630090415346545</v>
+        <v>-4.008052150699646</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.345464380631872</v>
       </c>
       <c r="E82">
-        <v>-11.42310946037413</v>
+        <v>-10.43729689669636</v>
       </c>
       <c r="F82">
-        <v>4.254203239172281</v>
+        <v>4.90105208327437</v>
       </c>
       <c r="G82">
-        <v>-3.765475236855089</v>
+        <v>-3.747336757845422</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.001644018850708</v>
       </c>
       <c r="E83">
-        <v>-12.78435063318381</v>
+        <v>-9.52867670095333</v>
       </c>
       <c r="F83">
-        <v>4.037778739886073</v>
+        <v>4.501506836397729</v>
       </c>
       <c r="G83">
-        <v>-3.652569081238245</v>
+        <v>-3.406423399302354</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.627879291094009</v>
       </c>
       <c r="E84">
-        <v>-12.87168678289574</v>
+        <v>-11.73230460866985</v>
       </c>
       <c r="F84">
-        <v>4.347128767466606</v>
+        <v>4.793491528615468</v>
       </c>
       <c r="G84">
-        <v>-2.925881161549444</v>
+        <v>-3.341314900181507</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.222894851698716</v>
       </c>
       <c r="E85">
-        <v>-15.14399352741259</v>
+        <v>-14.11709864753723</v>
       </c>
       <c r="F85">
-        <v>4.214534573402354</v>
+        <v>4.597067651335345</v>
       </c>
       <c r="G85">
-        <v>-2.56501183449565</v>
+        <v>-2.669373472075634</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.792160244623057</v>
       </c>
       <c r="E86">
-        <v>-15.56923535062887</v>
+        <v>-16.36147829284877</v>
       </c>
       <c r="F86">
-        <v>3.995929311070586</v>
+        <v>4.728082890601904</v>
       </c>
       <c r="G86">
-        <v>-3.411849383441219</v>
+        <v>-2.598706566994352</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.344524552770878</v>
       </c>
       <c r="E87">
-        <v>-16.35792344075275</v>
+        <v>-16.48303612063667</v>
       </c>
       <c r="F87">
-        <v>3.942827651725901</v>
+        <v>4.757398870802604</v>
       </c>
       <c r="G87">
-        <v>-1.965773296977711</v>
+        <v>-1.504432223352575</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.882034948575592</v>
       </c>
       <c r="E88">
-        <v>-18.17345659753791</v>
+        <v>-17.59511612507032</v>
       </c>
       <c r="F88">
-        <v>3.524526575692711</v>
+        <v>4.442998405057733</v>
       </c>
       <c r="G88">
-        <v>-1.928311163655319</v>
+        <v>-1.534452250302686</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.418848400645759</v>
       </c>
       <c r="E89">
-        <v>-19.49725634725217</v>
+        <v>-19.70410798297454</v>
       </c>
       <c r="F89">
-        <v>3.541741458993537</v>
+        <v>4.915373535867689</v>
       </c>
       <c r="G89">
-        <v>-1.747442818662777</v>
+        <v>-1.445799151306543</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.960807760186117</v>
       </c>
       <c r="E90">
-        <v>-20.71539321294546</v>
+        <v>-21.03599105879249</v>
       </c>
       <c r="F90">
-        <v>3.32686899150446</v>
+        <v>4.257202778176124</v>
       </c>
       <c r="G90">
-        <v>-1.691570741596497</v>
+        <v>-0.709911225564108</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.515156914623089</v>
       </c>
       <c r="E91">
-        <v>-22.32673294825076</v>
+        <v>-23.53869750387159</v>
       </c>
       <c r="F91">
-        <v>3.368441271784745</v>
+        <v>4.155923201177855</v>
       </c>
       <c r="G91">
-        <v>-1.165505192133069</v>
+        <v>-0.135677238504285</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.093002094864333</v>
       </c>
       <c r="E92">
-        <v>-23.82376947112845</v>
+        <v>-24.66996918114975</v>
       </c>
       <c r="F92">
-        <v>3.281535409675005</v>
+        <v>3.662709667932549</v>
       </c>
       <c r="G92">
-        <v>-0.881599427776251</v>
+        <v>0.9173642604458691</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.696178548282516</v>
       </c>
       <c r="E93">
-        <v>-27.74979341071437</v>
+        <v>-27.38569051507565</v>
       </c>
       <c r="F93">
-        <v>2.823982182527648</v>
+        <v>3.797386435275604</v>
       </c>
       <c r="G93">
-        <v>-0.4538305964648638</v>
+        <v>0.5846345704758792</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.333484786261905</v>
       </c>
       <c r="E94">
-        <v>-28.72135486669001</v>
+        <v>-29.26440494121583</v>
       </c>
       <c r="F94">
-        <v>2.545854917070003</v>
+        <v>3.205026576900126</v>
       </c>
       <c r="G94">
-        <v>0.2664712808786825</v>
+        <v>0.692022046678758</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.007162804737917</v>
       </c>
       <c r="E95">
-        <v>-31.00713382137967</v>
+        <v>-29.74098833849407</v>
       </c>
       <c r="F95">
-        <v>1.959807710473467</v>
+        <v>3.00438053964944</v>
       </c>
       <c r="G95">
-        <v>-0.8964935721574321</v>
+        <v>0.04943522586960272</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.713740055867644</v>
       </c>
       <c r="E96">
-        <v>-32.86397798229981</v>
+        <v>-33.7630680044937</v>
       </c>
       <c r="F96">
-        <v>1.867445981485038</v>
+        <v>2.817762969397717</v>
       </c>
       <c r="G96">
-        <v>0.1032415225193773</v>
+        <v>1.264041278772809</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.455968678674113</v>
       </c>
       <c r="E97">
-        <v>-34.90793416074288</v>
+        <v>-35.61109069804689</v>
       </c>
       <c r="F97">
-        <v>1.444294014232857</v>
+        <v>2.183778568446744</v>
       </c>
       <c r="G97">
-        <v>-0.08085129382841484</v>
+        <v>0.8856128181787192</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.22275260829647</v>
       </c>
       <c r="E98">
-        <v>-37.27702571598866</v>
+        <v>-37.39131534299424</v>
       </c>
       <c r="F98">
-        <v>0.9526451824320037</v>
+        <v>2.258748039071817</v>
       </c>
       <c r="G98">
-        <v>-0.3979518983075055</v>
+        <v>0.6534012224176202</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.01185500196105</v>
       </c>
       <c r="E99">
-        <v>-38.79768502352736</v>
+        <v>-40.46273698903764</v>
       </c>
       <c r="F99">
-        <v>0.8552076759845917</v>
+        <v>1.512341106301544</v>
       </c>
       <c r="G99">
-        <v>-0.5086863360505874</v>
+        <v>1.042132100729922</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.8101407011275105</v>
       </c>
       <c r="E100">
-        <v>-41.74571254557274</v>
+        <v>-43.2552453924746</v>
       </c>
       <c r="F100">
-        <v>0.3517348958190679</v>
+        <v>0.9937882784092051</v>
       </c>
       <c r="G100">
-        <v>-0.6843273296366202</v>
+        <v>-0.8864957246288331</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.6138569526195549</v>
       </c>
       <c r="E101">
-        <v>-43.62599382371958</v>
+        <v>-42.86548642734542</v>
       </c>
       <c r="F101">
-        <v>0.0808950531313176</v>
+        <v>1.128629751167466</v>
       </c>
       <c r="G101">
-        <v>-1.431378414937478</v>
+        <v>0.8965541711860104</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.404246166534223</v>
       </c>
       <c r="E102">
-        <v>-45.8775624215183</v>
+        <v>-46.9001099663463</v>
       </c>
       <c r="F102">
-        <v>-0.04154362675017924</v>
+        <v>0.2282398840919729</v>
       </c>
       <c r="G102">
-        <v>-0.7474197065240505</v>
+        <v>-0.1063623577540386</v>
       </c>
     </row>
   </sheetData>
